--- a/software/python_processing/results/Top Training Features.xlsx
+++ b/software/python_processing/results/Top Training Features.xlsx
@@ -1,40 +1,513 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="154">
+  <si>
+    <t>bvp_mean</t>
+  </si>
+  <si>
+    <t>bvp_std</t>
+  </si>
+  <si>
+    <t>bvp_min</t>
+  </si>
+  <si>
+    <t>bvp_max</t>
+  </si>
+  <si>
+    <t>bvp_ptp</t>
+  </si>
+  <si>
+    <t>bvp_sum</t>
+  </si>
+  <si>
+    <t>bvp_energy</t>
+  </si>
+  <si>
+    <t>bvp_skewness</t>
+  </si>
+  <si>
+    <t>bvp_kurtosis</t>
+  </si>
+  <si>
+    <t>bvp_peaks</t>
+  </si>
+  <si>
+    <t>bvp_rms</t>
+  </si>
+  <si>
+    <t>bvp_lineintegral</t>
+  </si>
+  <si>
+    <t>bvp_n_above_mean</t>
+  </si>
+  <si>
+    <t>bvp_n_below_mean</t>
+  </si>
+  <si>
+    <t>bvp_n_sign_changes</t>
+  </si>
+  <si>
+    <t>bvp_iqr</t>
+  </si>
+  <si>
+    <t>bvp_iqr_5_95</t>
+  </si>
+  <si>
+    <t>bvp_pct_5</t>
+  </si>
+  <si>
+    <t>bvp_pct_95</t>
+  </si>
+  <si>
+    <t>bvp_entropy</t>
+  </si>
+  <si>
+    <t>bvp_perm_entropy</t>
+  </si>
+  <si>
+    <t>bvp_svd_entropy</t>
+  </si>
+  <si>
+    <t>scl_mean</t>
+  </si>
+  <si>
+    <t>scl_std</t>
+  </si>
+  <si>
+    <t>scl_min</t>
+  </si>
+  <si>
+    <t>scl_max</t>
+  </si>
+  <si>
+    <t>scl_ptp</t>
+  </si>
+  <si>
+    <t>scl_sum</t>
+  </si>
+  <si>
+    <t>scl_energy</t>
+  </si>
+  <si>
+    <t>scl_skewness</t>
+  </si>
+  <si>
+    <t>scl_kurtosis</t>
+  </si>
+  <si>
+    <t>scl_peaks</t>
+  </si>
+  <si>
+    <t>scl_rms</t>
+  </si>
+  <si>
+    <t>scl_lineintegral</t>
+  </si>
+  <si>
+    <t>scl_n_above_mean</t>
+  </si>
+  <si>
+    <t>scl_n_below_mean</t>
+  </si>
+  <si>
+    <t>scl_n_sign_changes</t>
+  </si>
+  <si>
+    <t>scl_iqr</t>
+  </si>
+  <si>
+    <t>scl_iqr_5_95</t>
+  </si>
+  <si>
+    <t>scl_pct_5</t>
+  </si>
+  <si>
+    <t>scl_pct_95</t>
+  </si>
+  <si>
+    <t>scl_entropy</t>
+  </si>
+  <si>
+    <t>scl_perm_entropy</t>
+  </si>
+  <si>
+    <t>scl_svd_entropy</t>
+  </si>
+  <si>
+    <t>scr_mean</t>
+  </si>
+  <si>
+    <t>scr_std</t>
+  </si>
+  <si>
+    <t>scr_min</t>
+  </si>
+  <si>
+    <t>scr_max</t>
+  </si>
+  <si>
+    <t>scr_ptp</t>
+  </si>
+  <si>
+    <t>scr_sum</t>
+  </si>
+  <si>
+    <t>scr_energy</t>
+  </si>
+  <si>
+    <t>scr_skewness</t>
+  </si>
+  <si>
+    <t>scr_kurtosis</t>
+  </si>
+  <si>
+    <t>scr_peaks</t>
+  </si>
+  <si>
+    <t>scr_rms</t>
+  </si>
+  <si>
+    <t>scr_lineintegral</t>
+  </si>
+  <si>
+    <t>scr_n_above_mean</t>
+  </si>
+  <si>
+    <t>scr_n_below_mean</t>
+  </si>
+  <si>
+    <t>scr_n_sign_changes</t>
+  </si>
+  <si>
+    <t>scr_iqr</t>
+  </si>
+  <si>
+    <t>scr_iqr_5_95</t>
+  </si>
+  <si>
+    <t>scr_pct_5</t>
+  </si>
+  <si>
+    <t>scr_pct_95</t>
+  </si>
+  <si>
+    <t>scr_entropy</t>
+  </si>
+  <si>
+    <t>scr_perm_entropy</t>
+  </si>
+  <si>
+    <t>scr_svd_entropy</t>
+  </si>
+  <si>
+    <t>accx_mean</t>
+  </si>
+  <si>
+    <t>accx_std</t>
+  </si>
+  <si>
+    <t>accx_min</t>
+  </si>
+  <si>
+    <t>accx_max</t>
+  </si>
+  <si>
+    <t>accx_ptp</t>
+  </si>
+  <si>
+    <t>accx_sum</t>
+  </si>
+  <si>
+    <t>accx_energy</t>
+  </si>
+  <si>
+    <t>accx_skewness</t>
+  </si>
+  <si>
+    <t>accx_kurtosis</t>
+  </si>
+  <si>
+    <t>accx_peaks</t>
+  </si>
+  <si>
+    <t>accx_rms</t>
+  </si>
+  <si>
+    <t>accx_lineintegral</t>
+  </si>
+  <si>
+    <t>accx_n_above_mean</t>
+  </si>
+  <si>
+    <t>accx_n_below_mean</t>
+  </si>
+  <si>
+    <t>accx_n_sign_changes</t>
+  </si>
+  <si>
+    <t>accx_iqr</t>
+  </si>
+  <si>
+    <t>accx_iqr_5_95</t>
+  </si>
+  <si>
+    <t>accx_pct_5</t>
+  </si>
+  <si>
+    <t>accx_pct_95</t>
+  </si>
+  <si>
+    <t>accx_entropy</t>
+  </si>
+  <si>
+    <t>accx_perm_entropy</t>
+  </si>
+  <si>
+    <t>accx_svd_entropy</t>
+  </si>
+  <si>
+    <t>accy_mean</t>
+  </si>
+  <si>
+    <t>accy_std</t>
+  </si>
+  <si>
+    <t>accy_min</t>
+  </si>
+  <si>
+    <t>accy_max</t>
+  </si>
+  <si>
+    <t>accy_ptp</t>
+  </si>
+  <si>
+    <t>accy_sum</t>
+  </si>
+  <si>
+    <t>accy_energy</t>
+  </si>
+  <si>
+    <t>accy_skewness</t>
+  </si>
+  <si>
+    <t>accy_kurtosis</t>
+  </si>
+  <si>
+    <t>accy_peaks</t>
+  </si>
+  <si>
+    <t>accy_rms</t>
+  </si>
+  <si>
+    <t>accy_lineintegral</t>
+  </si>
+  <si>
+    <t>accy_n_above_mean</t>
+  </si>
+  <si>
+    <t>accy_n_below_mean</t>
+  </si>
+  <si>
+    <t>accy_n_sign_changes</t>
+  </si>
+  <si>
+    <t>accy_iqr</t>
+  </si>
+  <si>
+    <t>accy_iqr_5_95</t>
+  </si>
+  <si>
+    <t>accy_pct_5</t>
+  </si>
+  <si>
+    <t>accy_pct_95</t>
+  </si>
+  <si>
+    <t>accy_entropy</t>
+  </si>
+  <si>
+    <t>accy_perm_entropy</t>
+  </si>
+  <si>
+    <t>accy_svd_entropy</t>
+  </si>
+  <si>
+    <t>accz_mean</t>
+  </si>
+  <si>
+    <t>accz_std</t>
+  </si>
+  <si>
+    <t>accz_min</t>
+  </si>
+  <si>
+    <t>accz_max</t>
+  </si>
+  <si>
+    <t>accz_ptp</t>
+  </si>
+  <si>
+    <t>accz_sum</t>
+  </si>
+  <si>
+    <t>accz_energy</t>
+  </si>
+  <si>
+    <t>accz_skewness</t>
+  </si>
+  <si>
+    <t>accz_kurtosis</t>
+  </si>
+  <si>
+    <t>accz_peaks</t>
+  </si>
+  <si>
+    <t>accz_rms</t>
+  </si>
+  <si>
+    <t>accz_lineintegral</t>
+  </si>
+  <si>
+    <t>accz_n_above_mean</t>
+  </si>
+  <si>
+    <t>accz_n_below_mean</t>
+  </si>
+  <si>
+    <t>accz_n_sign_changes</t>
+  </si>
+  <si>
+    <t>accz_iqr</t>
+  </si>
+  <si>
+    <t>accz_iqr_5_95</t>
+  </si>
+  <si>
+    <t>accz_pct_5</t>
+  </si>
+  <si>
+    <t>accz_pct_95</t>
+  </si>
+  <si>
+    <t>accz_entropy</t>
+  </si>
+  <si>
+    <t>accz_perm_entropy</t>
+  </si>
+  <si>
+    <t>accz_svd_entropy</t>
+  </si>
+  <si>
+    <t>hrv_mean</t>
+  </si>
+  <si>
+    <t>hrv_std</t>
+  </si>
+  <si>
+    <t>hrv_min</t>
+  </si>
+  <si>
+    <t>hrv_max</t>
+  </si>
+  <si>
+    <t>hrv_ptp</t>
+  </si>
+  <si>
+    <t>hrv_sum</t>
+  </si>
+  <si>
+    <t>hrv_energy</t>
+  </si>
+  <si>
+    <t>hrv_skewness</t>
+  </si>
+  <si>
+    <t>hrv_kurtosis</t>
+  </si>
+  <si>
+    <t>hrv_peaks</t>
+  </si>
+  <si>
+    <t>hrv_rms</t>
+  </si>
+  <si>
+    <t>hrv_lineintegral</t>
+  </si>
+  <si>
+    <t>hrv_n_above_mean</t>
+  </si>
+  <si>
+    <t>hrv_n_below_mean</t>
+  </si>
+  <si>
+    <t>hrv_n_sign_changes</t>
+  </si>
+  <si>
+    <t>hrv_iqr</t>
+  </si>
+  <si>
+    <t>hrv_iqr_5_95</t>
+  </si>
+  <si>
+    <t>hrv_pct_5</t>
+  </si>
+  <si>
+    <t>hrv_pct_95</t>
+  </si>
+  <si>
+    <t>hrv_entropy</t>
+  </si>
+  <si>
+    <t>hrv_perm_entropy</t>
+  </si>
+  <si>
+    <t>hrv_svd_entropy</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,85 +515,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -408,14 +832,475 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A1"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="B1:EY1"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="2:155">
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BD1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="BE1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="BF1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="BG1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="BH1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="BI1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="BJ1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="BK1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="BL1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="BM1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="BN1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="BO1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="BP1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="BQ1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="BR1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BT1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BU1" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BV1" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="BW1" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BX1" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="BY1" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="BZ1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="CA1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="CB1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="CC1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="CD1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="CE1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="CF1" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="CG1" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="CH1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="CI1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="CJ1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="CK1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CL1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CM1" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="CN1" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CO1" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CP1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="CQ1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="CR1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="CS1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="CT1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="CU1" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="CV1" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="CW1" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="CX1" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="CY1" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="CZ1" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="DA1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="DB1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="DC1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="DD1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="DE1" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="DF1" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="DG1" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="DH1" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="DI1" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="DJ1" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="DK1" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="DL1" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="DM1" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="DN1" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="DO1" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="DP1" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="DQ1" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="DR1" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="DS1" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="DT1" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="DU1" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="DV1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="DW1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="DX1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="DY1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="DZ1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="EA1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="EB1" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="EC1" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="ED1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="EE1" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="EF1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="EG1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="EH1" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="EI1" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="EJ1" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="EK1" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="EL1" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="EM1" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="EN1" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="EO1" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="EP1" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="EQ1" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="ER1" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="ES1" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="ET1" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="EU1" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="EV1" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="EW1" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="EX1" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="EY1" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>